--- a/results/补充分析结果.xlsx
+++ b/results/补充分析结果.xlsx
@@ -16,10 +16,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4方案与理想基准" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结构敏感性" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="误差倍率压力测试" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="终端价值敏感性" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="费用执行诊断" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="结算歧义敏感性" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="尾部风险" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度配对差" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全题关键指标'!$A$1:$E$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q2参数敏感性'!$A$1:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q2参数敏感性'!$A$1:$O$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Q2参照方案'!$A$1:$K$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Q3八组信息消融'!$A$1:$Q$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Q3方案对比'!$A$1:$AB$11</definedName>
@@ -27,6 +32,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Q4方案与理想基准'!$A$1:$AA$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'结构敏感性'!$A$1:$T$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'误差倍率压力测试'!$A$1:$U$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'终端价值敏感性'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'费用执行诊断'!$A$1:$V$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'结算歧义敏感性'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'尾部风险'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'月度配对差'!$A$1:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +445,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -497,17 +507,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>F1-W30-alpha0.9</t>
+          <t>F1-W35-alpha0.805-H49</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="D3" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="E3" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
     </row>
     <row r="4">
@@ -522,13 +532,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14968496.84326568</v>
+        <v>14664345.39945607</v>
       </c>
       <c r="D4" t="n">
-        <v>22881901.5557863</v>
+        <v>21702916.77270221</v>
       </c>
       <c r="E4" t="n">
-        <v>87488.7580637784</v>
+        <v>210761.4751768127</v>
       </c>
     </row>
     <row r="5">
@@ -543,13 +553,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17258751.729631</v>
+        <v>17378687.69176505</v>
       </c>
       <c r="D5" t="n">
-        <v>22898507.45740178</v>
+        <v>21714014.40330241</v>
       </c>
       <c r="E5" t="n">
-        <v>425014.4958167563</v>
+        <v>570732.6617703987</v>
       </c>
     </row>
     <row r="6">
@@ -564,17 +574,1589 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15769829.13243304</v>
+        <v>15465962.60412982</v>
       </c>
       <c r="D6" t="n">
-        <v>22894661.79263044</v>
+        <v>21711144.64020411</v>
       </c>
       <c r="E6" t="n">
-        <v>86353.65372001668</v>
+        <v>210394.0223251306</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E6"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>终端价值倍率</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>现金费用_元</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>合同购电量_kWh</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>应急购电量_kWh</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>充电量_kWh</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>放电量_kWh</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>弃购量_kWh</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>期末SOC_kWh</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SOC下限触及比例</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>SOC上限触及比例</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>数值门禁</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>相对倍率1费用变化_元</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>相对倍率1费用变化_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>21869985.06147635</v>
+      </c>
+      <c r="C2" t="n">
+        <v>22231606.27750961</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1494646.58175811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4892842.984116627</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3963207.171251413</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2801690.113486523</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1294.781074074074</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1286910197869102</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7083883.708018858</v>
+      </c>
+      <c r="M2" t="n">
+        <v>47.9090704079504</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>14750539.87774745</v>
+      </c>
+      <c r="C3" t="n">
+        <v>22151481.39735274</v>
+      </c>
+      <c r="D3" t="n">
+        <v>257564.2850868242</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6618263.489394816</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5361107.952269627</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1508647.925907326</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1533.289629629629</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0490867579908675</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0869101978691019</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-35561.47571004368</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.2405061000189112</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>14786101.35345749</v>
+      </c>
+      <c r="C4" t="n">
+        <v>22382650.65499936</v>
+      </c>
+      <c r="D4" t="n">
+        <v>245483.2930631757</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7112133.945271054</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5760889.777650556</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1596110.942201504</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10731.90891</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0141742770167427</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1581050228310502</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>14786101.35345749</v>
+      </c>
+      <c r="C5" t="n">
+        <v>22382650.65499936</v>
+      </c>
+      <c r="D5" t="n">
+        <v>245483.2930631757</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7112133.945271054</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5760889.777650556</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1596110.942201504</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10731.90891</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0141742770167427</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1581050228310502</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>方案</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>口径A现金总费_元</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>计划费用A_元</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>调整费用_元</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>紧急费用_元</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>口径B现金总费_元</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>口径B相对A_元</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>计划购电量_kWh</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>最终合同量_kWh</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>调整量_kWh</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>应急购电量_kWh</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>弃购量_kWh</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>弃光量_kWh</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>充电量_kWh</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>放电量_kWh</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>期末SOC_kWh</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>SOC一步MAE_kWh</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>SOC一步RMSE_kWh</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>SOC一步最大绝对误差_kWh</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>充电一步MAE_kWh</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>放电一步MAE_kWh</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>费用加总误差_元</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q2-F1-W35-alpha0.805-H49</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14786101.35345749</v>
+      </c>
+      <c r="C2" t="n">
+        <v>13665855.74064841</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1120245.612809082</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14786101.35345749</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22382650.65499936</v>
+      </c>
+      <c r="I2" t="n">
+        <v>22382650.65499936</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>245483.2930631757</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1596110.942201504</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1741589.343273862</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7112133.945271054</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5760889.777650556</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10731.90891</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.32747094090384</v>
+      </c>
+      <c r="R2" t="n">
+        <v>19.66553798863036</v>
+      </c>
+      <c r="S2" t="n">
+        <v>284.5826746031753</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.261189371596436</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.963160455820343</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14664345.39945608</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12892887.15035176</v>
+      </c>
+      <c r="D3" t="n">
+        <v>859812.7911077078</v>
+      </c>
+      <c r="E3" t="n">
+        <v>911645.4579966022</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14991205.57384036</v>
+      </c>
+      <c r="G3" t="n">
+        <v>326860.1743842872</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21702724.36660489</v>
+      </c>
+      <c r="I3" t="n">
+        <v>21702916.77270221</v>
+      </c>
+      <c r="J3" t="n">
+        <v>192.4060973130291</v>
+      </c>
+      <c r="K3" t="n">
+        <v>210761.4751768127</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1228166.903903766</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1460023.595710788</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6769990.806830542</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5483692.553532739</v>
+      </c>
+      <c r="P3" t="n">
+        <v>10800</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.061882227023406</v>
+      </c>
+      <c r="R3" t="n">
+        <v>17.62707690128947</v>
+      </c>
+      <c r="S3" t="n">
+        <v>271.9788518518526</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.230206767699222</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.749226522484695</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q4-2-median30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17378687.69176505</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13948594.66055932</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3430093.031205731</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17378687.69176505</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21714014.40330241</v>
+      </c>
+      <c r="I4" t="n">
+        <v>21714014.40330241</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>570732.6617703987</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1520739.2390211</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1519070.008972429</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6872318.172127222</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5566569.850014608</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10800</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.79583923688331</v>
+      </c>
+      <c r="R4" t="n">
+        <v>17.30304533400997</v>
+      </c>
+      <c r="S4" t="n">
+        <v>271.9788518518526</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.007292950648069</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.690348023170043</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q4-3-median30</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>15465962.60412982</v>
+      </c>
+      <c r="C5" t="n">
+        <v>13606722.50373406</v>
+      </c>
+      <c r="D5" t="n">
+        <v>894288.7134629381</v>
+      </c>
+      <c r="E5" t="n">
+        <v>964951.3869328208</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15807140.27529378</v>
+      </c>
+      <c r="G5" t="n">
+        <v>341177.6711639591</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21712276.07168716</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21711144.64020411</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1131.431483051707</v>
+      </c>
+      <c r="K5" t="n">
+        <v>210394.0223251306</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1233536.134352993</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1452510.114575769</v>
+      </c>
+      <c r="N5" t="n">
+        <v>6822646.940177951</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5526344.021544142</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10800</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.156975405922769</v>
+      </c>
+      <c r="R5" t="n">
+        <v>18.06754074389078</v>
+      </c>
+      <c r="S5" t="n">
+        <v>271.9788518518526</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.220298959909139</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.842835707804089</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:V5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>方案</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>口径A总费_元</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>口径B总费_元</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>口径B-A_元</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>口径A排序</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>口径B排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14664345.39945608</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14991205.57384036</v>
+      </c>
+      <c r="E2" t="n">
+        <v>326860.1743842872</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>abl_none</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15230376.11791279</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15230376.11791279</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>abl_1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>15038617.00496167</v>
+      </c>
+      <c r="D4" t="n">
+        <v>15374206.12075535</v>
+      </c>
+      <c r="E4" t="n">
+        <v>335589.1157936824</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>abl_2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14746909.95868178</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14938335.51425038</v>
+      </c>
+      <c r="E5" t="n">
+        <v>191425.5555685973</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>abl_3</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>14805047.5356759</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14808406.7144361</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3359.178760199757</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>abl_1_2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>14679898.81845561</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15006308.565209</v>
+      </c>
+      <c r="E7" t="n">
+        <v>326409.7467533903</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>abl_1_3</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>14864586.67585926</v>
+      </c>
+      <c r="D8" t="n">
+        <v>15202066.21487794</v>
+      </c>
+      <c r="E8" t="n">
+        <v>337479.5390186841</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>abl_2_3</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>14710994.0917806</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14903974.86686867</v>
+      </c>
+      <c r="E9" t="n">
+        <v>192980.7750880698</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Q3主方案</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Q3主方案</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>14664345.39945608</v>
+      </c>
+      <c r="D10" t="n">
+        <v>14991205.57384036</v>
+      </c>
+      <c r="E10" t="n">
+        <v>326860.1743842872</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Q4-3_median30</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>15465962.60412982</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15807140.27529378</v>
+      </c>
+      <c r="E11" t="n">
+        <v>341177.6711639591</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>方案</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>日均费用_元</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VaR95_元</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CVaR95_元</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>最坏日费用_元</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>最坏日</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>最坏5日均费用_元</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q2-F1-W35-alpha0.805-H49</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>44269.76453130985</v>
+      </c>
+      <c r="C2" t="n">
+        <v>66075.34898232248</v>
+      </c>
+      <c r="D2" t="n">
+        <v>70048.63929377373</v>
+      </c>
+      <c r="E2" t="n">
+        <v>88726.18521099028</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>77444.4039043824</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>43905.22574687447</v>
+      </c>
+      <c r="C3" t="n">
+        <v>65177.29723913257</v>
+      </c>
+      <c r="D3" t="n">
+        <v>70474.33954651393</v>
+      </c>
+      <c r="E3" t="n">
+        <v>77111.50437334257</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>76229.43143185688</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q4-2-median30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>52031.99907714087</v>
+      </c>
+      <c r="C4" t="n">
+        <v>87294.39557126485</v>
+      </c>
+      <c r="D4" t="n">
+        <v>101705.2869464582</v>
+      </c>
+      <c r="E4" t="n">
+        <v>134220.6298287851</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>118629.1199991868</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q4-3-median30</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>46305.27725787371</v>
+      </c>
+      <c r="C5" t="n">
+        <v>76237.78600982552</v>
+      </c>
+      <c r="D5" t="n">
+        <v>83469.29159802229</v>
+      </c>
+      <c r="E5" t="n">
+        <v>92033.52525298508</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>90684.65772765179</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>方案A</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>方案B</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>方案A日均费用_元</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>方案B日均费用_元</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>天数</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>A相对B日均差_元</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>45843.7930370851</v>
+      </c>
+      <c r="E2" t="n">
+        <v>47055.07730266899</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-1211.284265583898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>38635.63005971807</v>
+      </c>
+      <c r="E3" t="n">
+        <v>41439.62159027584</v>
+      </c>
+      <c r="F3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2803.991530557767</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>34143.55270056849</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36570.94279797475</v>
+      </c>
+      <c r="F4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2427.390097406264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>34967.38476817256</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35582.84955237985</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-615.4647842072882</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>48203.08086012867</v>
+      </c>
+      <c r="E6" t="n">
+        <v>49901.71061877125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1698.629758642579</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>53918.06729314468</v>
+      </c>
+      <c r="E7" t="n">
+        <v>56808.00522113866</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-2889.937927993982</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>44692.9208187258</v>
+      </c>
+      <c r="E8" t="n">
+        <v>47152.43358886249</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-2459.512770136695</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>40977.56794394099</v>
+      </c>
+      <c r="E9" t="n">
+        <v>42355.20187241324</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-1377.633928472249</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>39031.7231831578</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40494.11399092157</v>
+      </c>
+      <c r="F10" t="n">
+        <v>31</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1462.390807763768</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>44826.2566922763</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45997.73268599121</v>
+      </c>
+      <c r="F11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1171.475993714907</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q3-S={6,12,18}</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Q3-空集</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>57664.12705483144</v>
+      </c>
+      <c r="E12" t="n">
+        <v>58138.01844943925</v>
+      </c>
+      <c r="F12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-473.8913946078173</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -585,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -598,10 +2180,11 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -675,28 +2258,33 @@
           <t>alpha</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="B2" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="C2" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="D2" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="E2" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="F2" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="G2" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="H2" t="n">
         <v>1200</v>
@@ -705,11 +2293,11 @@
         <v>10800</v>
       </c>
       <c r="J2" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>主配置 F1-W30-a0.9</t>
+          <t>主配置 F1-W35-a0.805-H49</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -718,33 +2306,36 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9</v>
+        <v>0.805</v>
+      </c>
+      <c r="O2" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14901640.7280058</v>
+        <v>14820043.33927402</v>
       </c>
       <c r="B3" t="n">
-        <v>22131288.74477963</v>
+        <v>22121216.77493607</v>
       </c>
       <c r="C3" t="n">
-        <v>7085763.630936125</v>
+        <v>7088489.44539288</v>
       </c>
       <c r="D3" t="n">
-        <v>5739532.506258762</v>
+        <v>5741740.415968733</v>
       </c>
       <c r="E3" t="n">
-        <v>1449484.192280575</v>
+        <v>1434789.507659145</v>
       </c>
       <c r="F3" t="n">
-        <v>302528.3206420797</v>
+        <v>289390.7044968469</v>
       </c>
       <c r="G3" t="n">
-        <v>7854</v>
+        <v>7785</v>
       </c>
       <c r="H3" t="n">
         <v>1200</v>
@@ -757,7 +2348,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>分位 a=0.8</t>
+          <t>分位 a=0.800</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -766,33 +2357,36 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N3" t="n">
         <v>0.8</v>
       </c>
+      <c r="O3" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15321486.97847276</v>
+        <v>14786818.42365214</v>
       </c>
       <c r="B4" t="n">
-        <v>24295276.17875265</v>
+        <v>22383624.75088721</v>
       </c>
       <c r="C4" t="n">
-        <v>7217204.404893992</v>
+        <v>7112089.799606251</v>
       </c>
       <c r="D4" t="n">
-        <v>5845984.497890634</v>
+        <v>5760854.019662064</v>
       </c>
       <c r="E4" t="n">
-        <v>2878010.133749682</v>
+        <v>1596986.704579956</v>
       </c>
       <c r="F4" t="n">
-        <v>72811.41692552294</v>
+        <v>245477.8510631757</v>
       </c>
       <c r="G4" t="n">
-        <v>2468</v>
+        <v>6822</v>
       </c>
       <c r="H4" t="n">
         <v>1200</v>
@@ -801,11 +2395,11 @@
         <v>10800</v>
       </c>
       <c r="J4" t="n">
-        <v>10745.633415</v>
+        <v>10731.90891</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>分位 a=0.95</t>
+          <t>分位 a=0.810</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -814,33 +2408,36 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N4" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14945243.27283704</v>
+        <v>14786354.18714403</v>
       </c>
       <c r="B5" t="n">
-        <v>23070425.99277577</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="C5" t="n">
-        <v>7160763.50985238</v>
+        <v>7112195.777930138</v>
       </c>
       <c r="D5" t="n">
-        <v>5800278.214135928</v>
+        <v>5760939.862104412</v>
       </c>
       <c r="E5" t="n">
-        <v>2038448.7017368</v>
+        <v>1596137.675988409</v>
       </c>
       <c r="F5" t="n">
-        <v>175554.4860886146</v>
+        <v>245523.9187057472</v>
       </c>
       <c r="G5" t="n">
-        <v>5048</v>
+        <v>6822</v>
       </c>
       <c r="H5" t="n">
         <v>1200</v>
@@ -849,11 +2446,11 @@
         <v>10800</v>
       </c>
       <c r="J5" t="n">
-        <v>10733.587605</v>
+        <v>10731.90891</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>窗口 W=21</t>
+          <t>时域 H=48</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -862,33 +2459,36 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9</v>
+        <v>0.805</v>
+      </c>
+      <c r="O5" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14973824.02802264</v>
+        <v>14786319.49659437</v>
       </c>
       <c r="B6" t="n">
-        <v>23389124.70695758</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="C6" t="n">
-        <v>7176722.368101954</v>
+        <v>7112080.202499186</v>
       </c>
       <c r="D6" t="n">
-        <v>5813200.119525084</v>
+        <v>5760846.246005341</v>
       </c>
       <c r="E6" t="n">
-        <v>2254571.818112036</v>
+        <v>1596156.843412747</v>
       </c>
       <c r="F6" t="n">
-        <v>135764.0991827842</v>
+        <v>245518.4343100805</v>
       </c>
       <c r="G6" t="n">
-        <v>3949</v>
+        <v>6823</v>
       </c>
       <c r="H6" t="n">
         <v>1200</v>
@@ -897,11 +2497,11 @@
         <v>10800</v>
       </c>
       <c r="J6" t="n">
-        <v>10738.887375</v>
+        <v>10731.90891</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>窗口 W=45</t>
+          <t>时域 H=50</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -910,33 +2510,36 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9</v>
+        <v>0.805</v>
+      </c>
+      <c r="O6" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>14824405.84656791</v>
+        <v>14837364.7710253</v>
       </c>
       <c r="B7" t="n">
-        <v>23026158.44873726</v>
+        <v>22441307.32866224</v>
       </c>
       <c r="C7" t="n">
-        <v>7175729.35764901</v>
+        <v>7111503.436319321</v>
       </c>
       <c r="D7" t="n">
-        <v>5812363.065495698</v>
+        <v>5760379.06539965</v>
       </c>
       <c r="E7" t="n">
-        <v>1984630.461862284</v>
+        <v>1644393.802915396</v>
       </c>
       <c r="F7" t="n">
-        <v>156748.6093239474</v>
+        <v>247334.5879051605</v>
       </c>
       <c r="G7" t="n">
-        <v>5163</v>
+        <v>6838</v>
       </c>
       <c r="H7" t="n">
         <v>1200</v>
@@ -945,46 +2548,49 @@
         <v>10800</v>
       </c>
       <c r="J7" t="n">
-        <v>10775.238</v>
+        <v>10731.90891</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>预测器 F2</t>
+          <t>窗口 W=30</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>30</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9</v>
+        <v>0.805</v>
+      </c>
+      <c r="O7" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17063107.41149379</v>
+        <v>14815783.48722026</v>
       </c>
       <c r="B8" t="n">
-        <v>25602542.80236549</v>
+        <v>22310747.49839211</v>
       </c>
       <c r="C8" t="n">
-        <v>6857711.744489918</v>
+        <v>7103022.545977281</v>
       </c>
       <c r="D8" t="n">
-        <v>5554815.68096954</v>
+        <v>5753511.028642097</v>
       </c>
       <c r="E8" t="n">
-        <v>4122612.02877938</v>
+        <v>1552826.522755021</v>
       </c>
       <c r="F8" t="n">
-        <v>235538.1830215846</v>
+        <v>260994.561156043</v>
       </c>
       <c r="G8" t="n">
-        <v>6202</v>
+        <v>7005</v>
       </c>
       <c r="H8" t="n">
         <v>1200</v>
@@ -993,27 +2599,132 @@
         <v>10800</v>
       </c>
       <c r="J8" t="n">
-        <v>10723.14674143831</v>
+        <v>10730.259555</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>窗口 W=45</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="O8" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14788842.57711093</v>
+      </c>
+      <c r="B9" t="n">
+        <v>22352957.23741948</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7116835.669079091</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5764671.769474064</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1585596.494889667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>249032.3770429062</v>
+      </c>
+      <c r="G9" t="n">
+        <v>7417</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10800</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10761.2472</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>预测器 F2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>35</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="O9" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>17345539.62800729</v>
+      </c>
+      <c r="B10" t="n">
+        <v>24791627.84610632</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6728408.914162049</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5450098.866662502</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3664839.288334678</v>
+      </c>
+      <c r="F10" t="n">
+        <v>403927.4088920049</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8801</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10800</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10702.61534306391</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>预测器 F0</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>F0</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>30</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.9</v>
+      <c r="M10" t="n">
+        <v>35</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="O10" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:O10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1037,7 +2748,7 @@
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1104,25 +2815,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="C2" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="D2" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="E2" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="F2" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="G2" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="H2" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="I2" t="n">
         <v>1200</v>
@@ -1131,7 +2842,7 @@
         <v>10800</v>
       </c>
       <c r="K2" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
     </row>
     <row r="3">
@@ -1234,10 +2945,10 @@
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
   </cols>
@@ -1346,13 +3057,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14968496.84326568</v>
+        <v>14664345.39945607</v>
       </c>
       <c r="E2" t="n">
-        <v>22886635.15205593</v>
+        <v>21702724.36660489</v>
       </c>
       <c r="F2" t="n">
-        <v>22881901.5557863</v>
+        <v>21702916.77270221</v>
       </c>
       <c r="G2" t="n">
         <v>1002</v>
@@ -1361,31 +3072,31 @@
         <v>1002</v>
       </c>
       <c r="I2" t="n">
-        <v>87488.7580637784</v>
+        <v>210761.4751768127</v>
       </c>
       <c r="J2" t="n">
-        <v>3331</v>
+        <v>7575</v>
       </c>
       <c r="K2" t="n">
-        <v>2058092.360053173</v>
+        <v>1228166.903903766</v>
       </c>
       <c r="L2" t="n">
         <v>10800</v>
       </c>
       <c r="M2" t="n">
-        <v>618746.7349360697</v>
+        <v>566030.7184567191</v>
       </c>
       <c r="N2" t="n">
-        <v>617.5117115130436</v>
+        <v>564.9009166234721</v>
       </c>
       <c r="O2" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P2" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q2" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
     <row r="3">
@@ -1405,13 +3116,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15587243.57820175</v>
+        <v>15230376.11791279</v>
       </c>
       <c r="E3" t="n">
-        <v>23937009.85731164</v>
+        <v>22173331.41516341</v>
       </c>
       <c r="F3" t="n">
-        <v>23937009.85731164</v>
+        <v>22173331.41516341</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1420,13 +3131,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>142668.7478688394</v>
+        <v>334601.055213179</v>
       </c>
       <c r="J3" t="n">
-        <v>2964</v>
+        <v>7298</v>
       </c>
       <c r="K3" t="n">
-        <v>2791107.695368104</v>
+        <v>1564867.417417239</v>
       </c>
       <c r="L3" t="n">
         <v>10800</v>
@@ -1435,13 +3146,13 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P3" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q3" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
     <row r="4">
@@ -1461,13 +3172,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15324029.74643886</v>
+        <v>15038617.00496167</v>
       </c>
       <c r="E4" t="n">
-        <v>23212522.08869002</v>
+        <v>21848661.15264621</v>
       </c>
       <c r="F4" t="n">
-        <v>23176400.39634803</v>
+        <v>21810858.66675233</v>
       </c>
       <c r="G4" t="n">
         <v>334</v>
@@ -1476,31 +3187,31 @@
         <v>334</v>
       </c>
       <c r="I4" t="n">
-        <v>113901.8896693575</v>
+        <v>266410.1203675859</v>
       </c>
       <c r="J4" t="n">
-        <v>3210</v>
+        <v>7466</v>
       </c>
       <c r="K4" t="n">
-        <v>2358779.495901326</v>
+        <v>1362713.964040545</v>
       </c>
       <c r="L4" t="n">
         <v>10800</v>
       </c>
       <c r="M4" t="n">
-        <v>263213.8317628857</v>
+        <v>191759.1129511241</v>
       </c>
       <c r="N4" t="n">
-        <v>788.0653645595379</v>
+        <v>574.1290806919883</v>
       </c>
       <c r="O4" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P4" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q4" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
     <row r="5">
@@ -1520,13 +3231,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15178645.35903143</v>
+        <v>14746909.95868178</v>
       </c>
       <c r="E5" t="n">
-        <v>23247894.99532724</v>
+        <v>21856979.60579322</v>
       </c>
       <c r="F5" t="n">
-        <v>23296983.35696664</v>
+        <v>21895603.68828719</v>
       </c>
       <c r="G5" t="n">
         <v>334</v>
@@ -1535,31 +3246,31 @@
         <v>334</v>
       </c>
       <c r="I5" t="n">
-        <v>86403.22089438923</v>
+        <v>224631.5554731863</v>
       </c>
       <c r="J5" t="n">
-        <v>2948</v>
+        <v>7326</v>
       </c>
       <c r="K5" t="n">
-        <v>2327679.401694986</v>
+        <v>1338628.056409965</v>
       </c>
       <c r="L5" t="n">
         <v>10800</v>
       </c>
       <c r="M5" t="n">
-        <v>408598.2191703208</v>
+        <v>483466.1592310145</v>
       </c>
       <c r="N5" t="n">
-        <v>1223.347961587787</v>
+        <v>1447.503470751541</v>
       </c>
       <c r="O5" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P5" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q5" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
     <row r="6">
@@ -1579,13 +3290,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15281353.41358723</v>
+        <v>14805047.5356759</v>
       </c>
       <c r="E6" t="n">
-        <v>23922276.24167073</v>
+        <v>22221681.60257166</v>
       </c>
       <c r="F6" t="n">
-        <v>23983190.82455487</v>
+        <v>22344531.66837451</v>
       </c>
       <c r="G6" t="n">
         <v>334</v>
@@ -1594,31 +3305,31 @@
         <v>334</v>
       </c>
       <c r="I6" t="n">
-        <v>95155.807646974</v>
+        <v>228882.1327726662</v>
       </c>
       <c r="J6" t="n">
-        <v>3046</v>
+        <v>7211</v>
       </c>
       <c r="K6" t="n">
-        <v>2661927.348206138</v>
+        <v>1561131.755069372</v>
       </c>
       <c r="L6" t="n">
-        <v>10792.23477907364</v>
+        <v>10800</v>
       </c>
       <c r="M6" t="n">
-        <v>305890.1646145228</v>
+        <v>425328.5822368935</v>
       </c>
       <c r="N6" t="n">
-        <v>915.8388162111462</v>
+        <v>1273.438868972735</v>
       </c>
       <c r="O6" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P6" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q6" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
     <row r="7">
@@ -1638,13 +3349,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15010282.40669226</v>
+        <v>14679898.81845561</v>
       </c>
       <c r="E7" t="n">
-        <v>22897627.64048758</v>
+        <v>21704637.15765034</v>
       </c>
       <c r="F7" t="n">
-        <v>22883641.41665446</v>
+        <v>21685745.12713859</v>
       </c>
       <c r="G7" t="n">
         <v>668</v>
@@ -1653,31 +3364,31 @@
         <v>668</v>
       </c>
       <c r="I7" t="n">
-        <v>92337.00850578332</v>
+        <v>217968.2830515631</v>
       </c>
       <c r="J7" t="n">
-        <v>3299</v>
+        <v>7540</v>
       </c>
       <c r="K7" t="n">
-        <v>2076124.463307304</v>
+        <v>1222531.272138724</v>
       </c>
       <c r="L7" t="n">
         <v>10800</v>
       </c>
       <c r="M7" t="n">
-        <v>576961.1715094857</v>
+        <v>550477.2994571794</v>
       </c>
       <c r="N7" t="n">
-        <v>863.7143286070145</v>
+        <v>824.0678135586518</v>
       </c>
       <c r="O7" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P7" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q7" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
     <row r="8">
@@ -1697,13 +3408,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15199272.58107305</v>
+        <v>14864586.67585925</v>
       </c>
       <c r="E8" t="n">
-        <v>23189712.85165236</v>
+        <v>21864471.80347794</v>
       </c>
       <c r="F8" t="n">
-        <v>23184730.51000738</v>
+        <v>21897603.00831374</v>
       </c>
       <c r="G8" t="n">
         <v>668</v>
@@ -1712,31 +3423,31 @@
         <v>668</v>
       </c>
       <c r="I8" t="n">
-        <v>96972.22305411096</v>
+        <v>218423.7412885823</v>
       </c>
       <c r="J8" t="n">
-        <v>3309</v>
+        <v>7491</v>
       </c>
       <c r="K8" t="n">
-        <v>2308496.461000985</v>
+        <v>1379168.471636407</v>
       </c>
       <c r="L8" t="n">
         <v>10800</v>
       </c>
       <c r="M8" t="n">
-        <v>387970.9971286953</v>
+        <v>365789.4420535397</v>
       </c>
       <c r="N8" t="n">
-        <v>580.7949058812803</v>
+        <v>547.5889851100893</v>
       </c>
       <c r="O8" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P8" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q8" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
     <row r="9">
@@ -1756,13 +3467,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15086848.61833207</v>
+        <v>14710994.0917806</v>
       </c>
       <c r="E9" t="n">
-        <v>23231935.89130968</v>
+        <v>21879972.62980549</v>
       </c>
       <c r="F9" t="n">
-        <v>23281575.36113922</v>
+        <v>21932634.79006909</v>
       </c>
       <c r="G9" t="n">
         <v>668</v>
@@ -1771,31 +3482,31 @@
         <v>668</v>
       </c>
       <c r="I9" t="n">
-        <v>81150.49726952834</v>
+        <v>212056.2914351403</v>
       </c>
       <c r="J9" t="n">
-        <v>3096</v>
+        <v>7335</v>
       </c>
       <c r="K9" t="n">
-        <v>2235196.294085561</v>
+        <v>1325666.912716498</v>
       </c>
       <c r="L9" t="n">
-        <v>10788.97682005759</v>
+        <v>10800</v>
       </c>
       <c r="M9" t="n">
-        <v>500394.9598696791</v>
+        <v>519382.0261321906</v>
       </c>
       <c r="N9" t="n">
-        <v>749.0942513019147</v>
+        <v>777.518003191902</v>
       </c>
       <c r="O9" t="n">
-        <v>158002.3479206534</v>
+        <v>61469.9513296159</v>
       </c>
       <c r="P9" t="n">
-        <v>286906.5229948629</v>
+        <v>284119.7665088866</v>
       </c>
       <c r="Q9" t="n">
-        <v>141057.4085265687</v>
+        <v>162707.0493100062</v>
       </c>
     </row>
   </sheetData>
@@ -1830,7 +3541,7 @@
     <col width="17" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
@@ -1988,7 +3699,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>主配置：分层储备 + H=36 + 三次调整</t>
+          <t>主配置：分层储备 + H=6 + 三次调整</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2002,40 +3713,40 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>1002</v>
       </c>
       <c r="F2" t="n">
-        <v>14968496.84326568</v>
+        <v>14664345.39945607</v>
       </c>
       <c r="G2" t="n">
-        <v>22886635.15205593</v>
+        <v>21702724.36660489</v>
       </c>
       <c r="H2" t="n">
-        <v>22881901.5557863</v>
+        <v>21702916.77270221</v>
       </c>
       <c r="I2" t="n">
-        <v>525660.0277627781</v>
+        <v>513849.9387485503</v>
       </c>
       <c r="J2" t="n">
-        <v>530393.6240324058</v>
+        <v>513657.5326512372</v>
       </c>
       <c r="K2" t="n">
-        <v>6733809.167002924</v>
+        <v>6769990.806830542</v>
       </c>
       <c r="L2" t="n">
-        <v>5454385.425272369</v>
+        <v>5483692.553532739</v>
       </c>
       <c r="M2" t="n">
-        <v>2058092.360053173</v>
+        <v>1228166.903903766</v>
       </c>
       <c r="N2" t="n">
-        <v>87488.7580637784</v>
+        <v>210761.4751768127</v>
       </c>
       <c r="O2" t="n">
-        <v>3331</v>
+        <v>7575</v>
       </c>
       <c r="P2" t="n">
         <v>1200</v>
@@ -2047,40 +3758,40 @@
         <v>10800</v>
       </c>
       <c r="S2" t="n">
-        <v>1652</v>
+        <v>3404</v>
       </c>
       <c r="T2" t="n">
-        <v>3948</v>
+        <v>3515</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>4.459999996470287</v>
+        <v>2.509500016458333</v>
       </c>
       <c r="W2" t="n">
-        <v>16.53112499479903</v>
+        <v>4.671475006034598</v>
       </c>
       <c r="X2" t="n">
-        <v>134.0705000038724</v>
+        <v>75.29219999560155</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
       <c r="Z2" t="n">
-        <v>52.86139132500156</v>
+        <v>84.89467907926583</v>
       </c>
       <c r="AA2" t="n">
-        <v>217.1732781867168</v>
+        <v>217.1344180151468</v>
       </c>
       <c r="AB2" t="n">
-        <v>296.7100240586232</v>
+        <v>296.6997658917641</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>对照：统一逐槽分位储备 + H=36</t>
+          <t>对照：统一逐槽分位储备 + H=6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2094,40 +3805,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>1002</v>
       </c>
       <c r="F3" t="n">
-        <v>14906791.435054</v>
+        <v>14655484.84410904</v>
       </c>
       <c r="G3" t="n">
-        <v>22679417.33892045</v>
+        <v>21809342.55225542</v>
       </c>
       <c r="H3" t="n">
-        <v>22674249.00465825</v>
+        <v>21798844.10777833</v>
       </c>
       <c r="I3" t="n">
-        <v>526065.7635395564</v>
+        <v>511973.7804028173</v>
       </c>
       <c r="J3" t="n">
-        <v>531234.0978017575</v>
+        <v>522472.2248799125</v>
       </c>
       <c r="K3" t="n">
-        <v>6751481.171367129</v>
+        <v>6775092.732256753</v>
       </c>
       <c r="L3" t="n">
-        <v>5468756.918593876</v>
+        <v>5487825.113127971</v>
       </c>
       <c r="M3" t="n">
-        <v>1888266.909242345</v>
+        <v>1284425.519491866</v>
       </c>
       <c r="N3" t="n">
-        <v>106350.115070942</v>
+        <v>195933.4369002257</v>
       </c>
       <c r="O3" t="n">
-        <v>4492</v>
+        <v>7528</v>
       </c>
       <c r="P3" t="n">
         <v>1200</v>
@@ -2136,37 +3847,37 @@
         <v>10800</v>
       </c>
       <c r="R3" t="n">
-        <v>10736.478015</v>
+        <v>10800</v>
       </c>
       <c r="S3" t="n">
-        <v>1849</v>
+        <v>3201</v>
       </c>
       <c r="T3" t="n">
-        <v>3810</v>
+        <v>3469</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>4.474650006159209</v>
+        <v>2.294000005349517</v>
       </c>
       <c r="W3" t="n">
-        <v>16.09704999282258</v>
+        <v>4.406924999784678</v>
       </c>
       <c r="X3" t="n">
-        <v>124.8901999788359</v>
+        <v>41.09969999990426</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8655189620758483</v>
+        <v>0.7736402195608783</v>
       </c>
       <c r="Z3" t="n">
-        <v>52.9435254839372</v>
+        <v>85.18632375685154</v>
       </c>
       <c r="AA3" t="n">
-        <v>217.1732781867168</v>
+        <v>217.1344180151468</v>
       </c>
       <c r="AB3" t="n">
-        <v>296.7100240586232</v>
+        <v>296.6997658917641</v>
       </c>
     </row>
     <row r="4">
@@ -2192,34 +3903,34 @@
         <v>1002</v>
       </c>
       <c r="F4" t="n">
-        <v>14966969.64848672</v>
+        <v>14731505.22714002</v>
       </c>
       <c r="G4" t="n">
-        <v>22886635.15205593</v>
+        <v>21709572.79394777</v>
       </c>
       <c r="H4" t="n">
-        <v>22880277.09804903</v>
+        <v>21734387.31087648</v>
       </c>
       <c r="I4" t="n">
-        <v>524127.8019401963</v>
+        <v>529579.9235717019</v>
       </c>
       <c r="J4" t="n">
-        <v>530485.8559470971</v>
+        <v>504765.4066429939</v>
       </c>
       <c r="K4" t="n">
-        <v>6734242.193440994</v>
+        <v>6734007.769752657</v>
       </c>
       <c r="L4" t="n">
-        <v>5454736.176687206</v>
+        <v>5454592.447799347</v>
       </c>
       <c r="M4" t="n">
-        <v>2058020.211713868</v>
+        <v>1236023.263275946</v>
       </c>
       <c r="N4" t="n">
-        <v>87755.20825595023</v>
+        <v>216642.5416707227</v>
       </c>
       <c r="O4" t="n">
-        <v>3337</v>
+        <v>7620</v>
       </c>
       <c r="P4" t="n">
         <v>1200</v>
@@ -2228,37 +3939,37 @@
         <v>10800</v>
       </c>
       <c r="R4" t="n">
-        <v>10800</v>
+        <v>10748.717444784</v>
       </c>
       <c r="S4" t="n">
-        <v>1654</v>
+        <v>3302</v>
       </c>
       <c r="T4" t="n">
-        <v>3948</v>
+        <v>3490</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6.447299994761124</v>
+        <v>5.550550005864352</v>
       </c>
       <c r="W4" t="n">
-        <v>21.56134999677306</v>
+        <v>16.22727500944166</v>
       </c>
       <c r="X4" t="n">
-        <v>127.2218000085559</v>
+        <v>77.02010002685711</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
       <c r="Z4" t="n">
-        <v>52.86139132500156</v>
+        <v>84.89467907926583</v>
       </c>
       <c r="AA4" t="n">
-        <v>217.1732781867168</v>
+        <v>217.1344180151468</v>
       </c>
       <c r="AB4" t="n">
-        <v>296.7100240586232</v>
+        <v>296.6997658917641</v>
       </c>
     </row>
     <row r="5">
@@ -2278,19 +3989,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>15587243.57820175</v>
+        <v>15230376.11791279</v>
       </c>
       <c r="G5" t="n">
-        <v>23937009.85731164</v>
+        <v>22173331.41516341</v>
       </c>
       <c r="H5" t="n">
-        <v>23937009.85731164</v>
+        <v>22173331.41516341</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2299,19 +4010,19 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7038381.753853209</v>
+        <v>7051469.359360761</v>
       </c>
       <c r="L5" t="n">
-        <v>5701089.2206211</v>
+        <v>5711690.181082217</v>
       </c>
       <c r="M5" t="n">
-        <v>2791107.695368104</v>
+        <v>1564867.417417239</v>
       </c>
       <c r="N5" t="n">
-        <v>142668.7478688394</v>
+        <v>334601.055213179</v>
       </c>
       <c r="O5" t="n">
-        <v>2964</v>
+        <v>7298</v>
       </c>
       <c r="P5" t="n">
         <v>1200</v>
@@ -2323,34 +4034,34 @@
         <v>10800</v>
       </c>
       <c r="S5" t="n">
-        <v>1986</v>
+        <v>3691</v>
       </c>
       <c r="T5" t="n">
-        <v>4051</v>
+        <v>3792</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4.263750015525147</v>
+        <v>2.360050013521686</v>
       </c>
       <c r="W5" t="n">
-        <v>16.34972498868592</v>
+        <v>4.383325001981575</v>
       </c>
       <c r="X5" t="n">
-        <v>118.1781999766827</v>
+        <v>45.40249999263324</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8968937125748503</v>
+        <v>0.771477877578177</v>
       </c>
       <c r="Z5" t="n">
-        <v>78.27435296100924</v>
+        <v>123.1293080374646</v>
       </c>
       <c r="AA5" t="n">
-        <v>310.9907294550483</v>
+        <v>310.6020004810514</v>
       </c>
       <c r="AB5" t="n">
-        <v>455.1455650513666</v>
+        <v>455.025712496879</v>
       </c>
     </row>
     <row r="6">
@@ -2370,40 +4081,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>334</v>
       </c>
       <c r="F6" t="n">
-        <v>15324029.74643886</v>
+        <v>15038617.00496167</v>
       </c>
       <c r="G6" t="n">
-        <v>23212522.08869002</v>
+        <v>21848661.15264621</v>
       </c>
       <c r="H6" t="n">
-        <v>23176400.39634803</v>
+        <v>21810858.66675233</v>
       </c>
       <c r="I6" t="n">
-        <v>498880.2535480225</v>
+        <v>480921.1863864739</v>
       </c>
       <c r="J6" t="n">
-        <v>535001.9458900057</v>
+        <v>518723.6722803506</v>
       </c>
       <c r="K6" t="n">
-        <v>6709892.068287106</v>
+        <v>6752775.164346841</v>
       </c>
       <c r="L6" t="n">
-        <v>5435012.575312557</v>
+        <v>5469747.883120941</v>
       </c>
       <c r="M6" t="n">
-        <v>2358779.495901326</v>
+        <v>1362713.964040545</v>
       </c>
       <c r="N6" t="n">
-        <v>113901.8896693575</v>
+        <v>266410.1203675859</v>
       </c>
       <c r="O6" t="n">
-        <v>3210</v>
+        <v>7466</v>
       </c>
       <c r="P6" t="n">
         <v>1200</v>
@@ -2415,34 +4126,34 @@
         <v>10800</v>
       </c>
       <c r="S6" t="n">
-        <v>1842</v>
+        <v>3649</v>
       </c>
       <c r="T6" t="n">
-        <v>4058</v>
+        <v>3716</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>4.550849989755079</v>
+        <v>2.960300000268034</v>
       </c>
       <c r="W6" t="n">
-        <v>16.58454999414971</v>
+        <v>8.118774981994648</v>
       </c>
       <c r="X6" t="n">
-        <v>100.2684000122826</v>
+        <v>52.82320000696927</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8947105788423154</v>
+        <v>0.76916999334664</v>
       </c>
       <c r="Z6" t="n">
-        <v>60.37254814766962</v>
+        <v>96.45946274652395</v>
       </c>
       <c r="AA6" t="n">
-        <v>245.2407902146633</v>
+        <v>245.1719698377312</v>
       </c>
       <c r="AB6" t="n">
-        <v>341.7932738426283</v>
+        <v>341.4936871574619</v>
       </c>
     </row>
     <row r="7">
@@ -2462,40 +4173,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>334</v>
       </c>
       <c r="F7" t="n">
-        <v>15178645.35903143</v>
+        <v>14746909.95868178</v>
       </c>
       <c r="G7" t="n">
-        <v>23247894.99532724</v>
+        <v>21856979.60579322</v>
       </c>
       <c r="H7" t="n">
-        <v>23296983.35696664</v>
+        <v>21895603.68828719</v>
       </c>
       <c r="I7" t="n">
-        <v>342749.859983788</v>
+        <v>320575.0443048602</v>
       </c>
       <c r="J7" t="n">
-        <v>293661.4983443889</v>
+        <v>281950.9618108911</v>
       </c>
       <c r="K7" t="n">
-        <v>6843461.078269294</v>
+        <v>6914990.55662027</v>
       </c>
       <c r="L7" t="n">
-        <v>5543203.473398129</v>
+        <v>5601142.350862419</v>
       </c>
       <c r="M7" t="n">
-        <v>2327679.401694986</v>
+        <v>1338628.056409965</v>
       </c>
       <c r="N7" t="n">
-        <v>86403.22089438923</v>
+        <v>224631.5554731863</v>
       </c>
       <c r="O7" t="n">
-        <v>2948</v>
+        <v>7326</v>
       </c>
       <c r="P7" t="n">
         <v>1200</v>
@@ -2507,34 +4218,34 @@
         <v>10800</v>
       </c>
       <c r="S7" t="n">
-        <v>1839</v>
+        <v>3767</v>
       </c>
       <c r="T7" t="n">
-        <v>3976</v>
+        <v>3673</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>4.491900006541982</v>
+        <v>3.066499994019978</v>
       </c>
       <c r="W7" t="n">
-        <v>16.28565001010429</v>
+        <v>8.27319998643361</v>
       </c>
       <c r="X7" t="n">
-        <v>191.3136999937706</v>
+        <v>42.88880000240169</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8953759148369926</v>
+        <v>0.7690244510978044</v>
       </c>
       <c r="Z7" t="n">
-        <v>62.74748750116346</v>
+        <v>98.86130633995116</v>
       </c>
       <c r="AA7" t="n">
-        <v>251.443197084939</v>
+        <v>251.0954265994333</v>
       </c>
       <c r="AB7" t="n">
-        <v>360.6052977611312</v>
+        <v>360.3373979082778</v>
       </c>
     </row>
     <row r="8">
@@ -2554,40 +4265,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>334</v>
       </c>
       <c r="F8" t="n">
-        <v>15281353.41358723</v>
+        <v>14805047.5356759</v>
       </c>
       <c r="G8" t="n">
-        <v>23922276.24167073</v>
+        <v>22221681.60257166</v>
       </c>
       <c r="H8" t="n">
-        <v>23983190.82455487</v>
+        <v>22344531.66837451</v>
       </c>
       <c r="I8" t="n">
-        <v>65781.28415236143</v>
+        <v>125764.3687397411</v>
       </c>
       <c r="J8" t="n">
-        <v>4866.701268223999</v>
+        <v>2914.302936893233</v>
       </c>
       <c r="K8" t="n">
-        <v>7178128.552720444</v>
+        <v>7103728.673923891</v>
       </c>
       <c r="L8" t="n">
-        <v>5814291.116402394</v>
+        <v>5754020.225878352</v>
       </c>
       <c r="M8" t="n">
-        <v>2661927.348206138</v>
+        <v>1561131.755069372</v>
       </c>
       <c r="N8" t="n">
-        <v>95155.807646974</v>
+        <v>228882.1327726662</v>
       </c>
       <c r="O8" t="n">
-        <v>3046</v>
+        <v>7211</v>
       </c>
       <c r="P8" t="n">
         <v>1200</v>
@@ -2596,37 +4307,37 @@
         <v>10800</v>
       </c>
       <c r="R8" t="n">
-        <v>10792.23477907364</v>
+        <v>10800</v>
       </c>
       <c r="S8" t="n">
-        <v>1892</v>
+        <v>3719</v>
       </c>
       <c r="T8" t="n">
-        <v>3951</v>
+        <v>3397</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4.76709999202285</v>
+        <v>3.142350004054606</v>
       </c>
       <c r="W8" t="n">
-        <v>16.18885000789305</v>
+        <v>8.012125006644055</v>
       </c>
       <c r="X8" t="n">
-        <v>101.3710999977775</v>
+        <v>37.08920002100058</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.8952511643379907</v>
+        <v>0.7702095808383234</v>
       </c>
       <c r="Z8" t="n">
-        <v>75.78254602634895</v>
+        <v>121.2714819458593</v>
       </c>
       <c r="AA8" t="n">
-        <v>310.9261684697503</v>
+        <v>310.5315425411475</v>
       </c>
       <c r="AB8" t="n">
-        <v>455.1071918495765</v>
+        <v>454.9828521824674</v>
       </c>
     </row>
     <row r="9">
@@ -2646,40 +4357,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>668</v>
       </c>
       <c r="F9" t="n">
-        <v>15010282.40669226</v>
+        <v>14679898.81845561</v>
       </c>
       <c r="G9" t="n">
-        <v>22897627.64048758</v>
+        <v>21704637.15765034</v>
       </c>
       <c r="H9" t="n">
-        <v>22883641.41665446</v>
+        <v>21685745.12713859</v>
       </c>
       <c r="I9" t="n">
-        <v>515315.9482908705</v>
+        <v>493794.5450236643</v>
       </c>
       <c r="J9" t="n">
-        <v>529302.172123994</v>
+        <v>512686.5755354124</v>
       </c>
       <c r="K9" t="n">
-        <v>6713082.01605152</v>
+        <v>6769575.1339307</v>
       </c>
       <c r="L9" t="n">
-        <v>5437596.433001731</v>
+        <v>5483355.858483868</v>
       </c>
       <c r="M9" t="n">
-        <v>2076124.463307304</v>
+        <v>1222531.272138724</v>
       </c>
       <c r="N9" t="n">
-        <v>92337.00850578332</v>
+        <v>217968.2830515631</v>
       </c>
       <c r="O9" t="n">
-        <v>3299</v>
+        <v>7540</v>
       </c>
       <c r="P9" t="n">
         <v>1200</v>
@@ -2691,34 +4402,34 @@
         <v>10800</v>
       </c>
       <c r="S9" t="n">
-        <v>1713</v>
+        <v>3440</v>
       </c>
       <c r="T9" t="n">
-        <v>3990</v>
+        <v>3607</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>4.226149991154671</v>
+        <v>2.339200000278652</v>
       </c>
       <c r="W9" t="n">
-        <v>12.5633000061498</v>
+        <v>4.935325006954372</v>
       </c>
       <c r="X9" t="n">
-        <v>81.59689998137765</v>
+        <v>101.1683999968227</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.893920492348636</v>
+        <v>0.7695234530938124</v>
       </c>
       <c r="Z9" t="n">
-        <v>52.98089379164013</v>
+        <v>84.93296785057298</v>
       </c>
       <c r="AA9" t="n">
-        <v>217.1883718808679</v>
+        <v>217.1491440226457</v>
       </c>
       <c r="AB9" t="n">
-        <v>296.7464094423171</v>
+        <v>296.7339941289505</v>
       </c>
     </row>
     <row r="10">
@@ -2738,40 +4449,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>668</v>
       </c>
       <c r="F10" t="n">
-        <v>15199272.58107305</v>
+        <v>14864586.67585925</v>
       </c>
       <c r="G10" t="n">
-        <v>23189712.85165236</v>
+        <v>21864471.80347794</v>
       </c>
       <c r="H10" t="n">
-        <v>23184730.51000738</v>
+        <v>21897603.00831374</v>
       </c>
       <c r="I10" t="n">
-        <v>533402.6042388419</v>
+        <v>553914.5465619932</v>
       </c>
       <c r="J10" t="n">
-        <v>538384.9458838217</v>
+        <v>520783.341726195</v>
       </c>
       <c r="K10" t="n">
-        <v>6779734.695917074</v>
+        <v>6771897.87176297</v>
       </c>
       <c r="L10" t="n">
-        <v>5491585.103692831</v>
+        <v>5485237.276128005</v>
       </c>
       <c r="M10" t="n">
-        <v>2308496.461000985</v>
+        <v>1379168.471636407</v>
       </c>
       <c r="N10" t="n">
-        <v>96972.22305411096</v>
+        <v>218423.7412885823</v>
       </c>
       <c r="O10" t="n">
-        <v>3309</v>
+        <v>7491</v>
       </c>
       <c r="P10" t="n">
         <v>1200</v>
@@ -2783,34 +4494,34 @@
         <v>10800</v>
       </c>
       <c r="S10" t="n">
-        <v>1735</v>
+        <v>3545</v>
       </c>
       <c r="T10" t="n">
-        <v>3953</v>
+        <v>3479</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.708950011059642</v>
+        <v>2.308100010850467</v>
       </c>
       <c r="W10" t="n">
-        <v>6.828825018601492</v>
+        <v>4.327799986640457</v>
       </c>
       <c r="X10" t="n">
-        <v>80.63279997440986</v>
+        <v>40.15869999420829</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.89416999334664</v>
+        <v>0.7686086161011311</v>
       </c>
       <c r="Z10" t="n">
-        <v>59.56539548686931</v>
+        <v>95.94870501489028</v>
       </c>
       <c r="AA10" t="n">
-        <v>245.165872130392</v>
+        <v>245.0989158293789</v>
       </c>
       <c r="AB10" t="n">
-        <v>341.7240263032683</v>
+        <v>341.4275067050504</v>
       </c>
     </row>
     <row r="11">
@@ -2830,40 +4541,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>668</v>
       </c>
       <c r="F11" t="n">
-        <v>15086848.61833207</v>
+        <v>14710994.0917806</v>
       </c>
       <c r="G11" t="n">
-        <v>23231935.89130968</v>
+        <v>21879972.62980549</v>
       </c>
       <c r="H11" t="n">
-        <v>23281575.36113922</v>
+        <v>21932634.79006909</v>
       </c>
       <c r="I11" t="n">
-        <v>347518.56613078</v>
+        <v>337600.7857481551</v>
       </c>
       <c r="J11" t="n">
-        <v>297879.0963012357</v>
+        <v>284938.6254845585</v>
       </c>
       <c r="K11" t="n">
-        <v>6912046.617449828</v>
+        <v>6940557.190209297</v>
       </c>
       <c r="L11" t="n">
-        <v>5598767.680996308</v>
+        <v>5621851.324069531</v>
       </c>
       <c r="M11" t="n">
-        <v>2235196.294085561</v>
+        <v>1325666.912716498</v>
       </c>
       <c r="N11" t="n">
-        <v>81150.49726952834</v>
+        <v>212056.2914351403</v>
       </c>
       <c r="O11" t="n">
-        <v>3096</v>
+        <v>7335</v>
       </c>
       <c r="P11" t="n">
         <v>1200</v>
@@ -2872,37 +4583,37 @@
         <v>10800</v>
       </c>
       <c r="R11" t="n">
-        <v>10788.97682005759</v>
+        <v>10800</v>
       </c>
       <c r="S11" t="n">
-        <v>1796</v>
+        <v>3732</v>
       </c>
       <c r="T11" t="n">
-        <v>3915</v>
+        <v>3451</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>4.02330000360962</v>
+        <v>2.281199995195493</v>
       </c>
       <c r="W11" t="n">
-        <v>6.818474997999147</v>
+        <v>4.129150001972448</v>
       </c>
       <c r="X11" t="n">
-        <v>88.76669997698627</v>
+        <v>102.979100018274</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8939620758483033</v>
+        <v>0.7693779108449768</v>
       </c>
       <c r="Z11" t="n">
-        <v>61.41432748224054</v>
+        <v>98.10883694608702</v>
       </c>
       <c r="AA11" t="n">
-        <v>251.4281033907878</v>
+        <v>251.0807005919345</v>
       </c>
       <c r="AB11" t="n">
-        <v>360.5753563866443</v>
+        <v>360.3092118442382</v>
       </c>
     </row>
   </sheetData>
@@ -3318,13 +5029,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>17264915.92481264</v>
+        <v>17402307.33424146</v>
       </c>
       <c r="G2" t="n">
-        <v>22979660.62141077</v>
+        <v>21794561.97872843</v>
       </c>
       <c r="H2" t="n">
-        <v>22979660.62141077</v>
+        <v>21794561.97872843</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -3333,19 +5044,19 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>7194459.136390725</v>
+        <v>7294734.138924334</v>
       </c>
       <c r="L2" t="n">
-        <v>5827511.900476488</v>
+        <v>5908726.783120269</v>
       </c>
       <c r="M2" t="n">
-        <v>2272636.79507344</v>
+        <v>1517080.51009965</v>
       </c>
       <c r="N2" t="n">
-        <v>421454.1250538519</v>
+        <v>567603.9400282265</v>
       </c>
       <c r="O2" t="n">
-        <v>4652</v>
+        <v>7815</v>
       </c>
       <c r="P2" t="n">
         <v>1200</v>
@@ -3360,28 +5071,28 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1577</v>
+        <v>3512</v>
       </c>
       <c r="U2" t="n">
-        <v>4341</v>
+        <v>3738</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>4.596099985064939</v>
+        <v>2.456700007314794</v>
       </c>
       <c r="X2" t="n">
-        <v>16.69132499955595</v>
+        <v>4.674925003200769</v>
       </c>
       <c r="Y2" t="n">
-        <v>121.65559999994</v>
+        <v>45.1564000104554</v>
       </c>
       <c r="Z2" t="n">
         <v>0.08432593978709239</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="3">
@@ -3411,13 +5122,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17337826.57173467</v>
+        <v>17390589.19644691</v>
       </c>
       <c r="G3" t="n">
-        <v>22907443.02233832</v>
+        <v>21722569.75849669</v>
       </c>
       <c r="H3" t="n">
-        <v>22907443.02233832</v>
+        <v>21722569.75849669</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -3426,19 +5137,19 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>6786685.515398353</v>
+        <v>6911489.860604851</v>
       </c>
       <c r="L3" t="n">
-        <v>5497215.267472666</v>
+        <v>5598298.917681486</v>
       </c>
       <c r="M3" t="n">
-        <v>2296846.165103692</v>
+        <v>1524399.271596943</v>
       </c>
       <c r="N3" t="n">
-        <v>440013.2832148161</v>
+        <v>574481.2215299479</v>
       </c>
       <c r="O3" t="n">
-        <v>4674</v>
+        <v>7944</v>
       </c>
       <c r="P3" t="n">
         <v>1200</v>
@@ -3453,28 +5164,28 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1541</v>
+        <v>3390</v>
       </c>
       <c r="U3" t="n">
-        <v>3854</v>
+        <v>3338</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>4.509849997702986</v>
+        <v>2.585549998912029</v>
       </c>
       <c r="X3" t="n">
-        <v>16.31087498390116</v>
+        <v>4.83590000658296</v>
       </c>
       <c r="Y3" t="n">
-        <v>127.8461000183597</v>
+        <v>41.23339999932796</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0826692834568957</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="4">
@@ -3504,13 +5215,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>17338929.32720425</v>
+        <v>17400942.40398221</v>
       </c>
       <c r="G4" t="n">
-        <v>22901256.72411335</v>
+        <v>21716615.41246375</v>
       </c>
       <c r="H4" t="n">
-        <v>22901256.72411335</v>
+        <v>21716615.41246375</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -3519,19 +5230,19 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6758274.202064989</v>
+        <v>6882879.156899542</v>
       </c>
       <c r="L4" t="n">
-        <v>5474202.103672642</v>
+        <v>5575124.247680186</v>
       </c>
       <c r="M4" t="n">
-        <v>2297539.868620977</v>
+        <v>1526933.542976867</v>
       </c>
       <c r="N4" t="n">
-        <v>439713.4696592768</v>
+        <v>576148.0195547844</v>
       </c>
       <c r="O4" t="n">
-        <v>4695</v>
+        <v>7952</v>
       </c>
       <c r="P4" t="n">
         <v>1200</v>
@@ -3546,28 +5257,28 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1544</v>
+        <v>3393</v>
       </c>
       <c r="U4" t="n">
-        <v>3818</v>
+        <v>3277</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>4.435850016307086</v>
+        <v>2.514899999368936</v>
       </c>
       <c r="X4" t="n">
-        <v>16.80257500993321</v>
+        <v>4.720124998129904</v>
       </c>
       <c r="Y4" t="n">
-        <v>119.7464000142645</v>
+        <v>51.29140001372434</v>
       </c>
       <c r="Z4" t="n">
         <v>0.0874769348802395</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="5">
@@ -3597,13 +5308,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17258751.729631</v>
+        <v>17378687.69176505</v>
       </c>
       <c r="G5" t="n">
-        <v>22898507.45740178</v>
+        <v>21714014.40330241</v>
       </c>
       <c r="H5" t="n">
-        <v>22898507.45740178</v>
+        <v>21714014.40330241</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3612,19 +5323,19 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6762132.110567249</v>
+        <v>6872318.172127222</v>
       </c>
       <c r="L5" t="n">
-        <v>5477327.009559472</v>
+        <v>5566569.850014608</v>
       </c>
       <c r="M5" t="n">
-        <v>2281458.906596703</v>
+        <v>1520739.2390211</v>
       </c>
       <c r="N5" t="n">
-        <v>425014.4958167563</v>
+        <v>570732.6617703987</v>
       </c>
       <c r="O5" t="n">
-        <v>4646</v>
+        <v>7932</v>
       </c>
       <c r="P5" t="n">
         <v>1200</v>
@@ -3639,28 +5350,28 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1558</v>
+        <v>3409</v>
       </c>
       <c r="U5" t="n">
-        <v>3848</v>
+        <v>3312</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>4.299299995182082</v>
+        <v>2.55129998549819</v>
       </c>
       <c r="X5" t="n">
-        <v>16.05447499605361</v>
+        <v>4.73490000149468</v>
       </c>
       <c r="Y5" t="n">
-        <v>154.4932000106201</v>
+        <v>41.3053999945987</v>
       </c>
       <c r="Z5" t="n">
         <v>0.08327562063373251</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="6">
@@ -3690,34 +5401,34 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15790185.29175134</v>
+        <v>15485837.97504129</v>
       </c>
       <c r="G6" t="n">
-        <v>22978999.17848023</v>
+        <v>21790407.76223825</v>
       </c>
       <c r="H6" t="n">
-        <v>22967804.61493134</v>
+        <v>21783823.91667556</v>
       </c>
       <c r="I6" t="n">
-        <v>517265.9748735852</v>
+        <v>505217.7896892817</v>
       </c>
       <c r="J6" t="n">
-        <v>528460.5384224707</v>
+        <v>511801.6352519834</v>
       </c>
       <c r="K6" t="n">
-        <v>7237922.519340141</v>
+        <v>7254274.499405099</v>
       </c>
       <c r="L6" t="n">
-        <v>5862717.240665515</v>
+        <v>5875962.34451813</v>
       </c>
       <c r="M6" t="n">
-        <v>2060832.78159649</v>
+        <v>1222723.163612793</v>
       </c>
       <c r="N6" t="n">
-        <v>85775.42891681503</v>
+        <v>207255.7216058667</v>
       </c>
       <c r="O6" t="n">
-        <v>3268</v>
+        <v>7431</v>
       </c>
       <c r="P6" t="n">
         <v>1200</v>
@@ -3732,28 +5443,28 @@
         <v>1002</v>
       </c>
       <c r="T6" t="n">
-        <v>1701</v>
+        <v>3483</v>
       </c>
       <c r="U6" t="n">
-        <v>4476</v>
+        <v>3967</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>4.612249991623685</v>
+        <v>3.142250003293157</v>
       </c>
       <c r="X6" t="n">
-        <v>16.82017498387722</v>
+        <v>8.390200004214421</v>
       </c>
       <c r="Y6" t="n">
-        <v>160.1334000006318</v>
+        <v>45.6984999764245</v>
       </c>
       <c r="Z6" t="n">
         <v>0.08432593978709239</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="7">
@@ -3783,34 +5494,34 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>15754516.51654786</v>
+        <v>15454638.39786348</v>
       </c>
       <c r="G7" t="n">
-        <v>22907423.61347442</v>
+        <v>21721379.73244404</v>
       </c>
       <c r="H7" t="n">
-        <v>22898688.77873048</v>
+        <v>21716491.71608075</v>
       </c>
       <c r="I7" t="n">
-        <v>523603.086077151</v>
+        <v>508900.6085165495</v>
       </c>
       <c r="J7" t="n">
-        <v>532337.9208210963</v>
+        <v>513788.624879831</v>
       </c>
       <c r="K7" t="n">
-        <v>6843971.997730376</v>
+        <v>6866908.281680874</v>
       </c>
       <c r="L7" t="n">
-        <v>5543617.318161605</v>
+        <v>5562195.708161508</v>
       </c>
       <c r="M7" t="n">
-        <v>2068035.903125989</v>
+        <v>1231275.76247419</v>
       </c>
       <c r="N7" t="n">
-        <v>86347.11351529999</v>
+        <v>210463.544176621</v>
       </c>
       <c r="O7" t="n">
-        <v>3317</v>
+        <v>7554</v>
       </c>
       <c r="P7" t="n">
         <v>1200</v>
@@ -3825,28 +5536,28 @@
         <v>1002</v>
       </c>
       <c r="T7" t="n">
-        <v>1657</v>
+        <v>3390</v>
       </c>
       <c r="U7" t="n">
-        <v>3987</v>
+        <v>3573</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>4.52479999512434</v>
+        <v>3.222949992050417</v>
       </c>
       <c r="X7" t="n">
-        <v>16.17935000103898</v>
+        <v>8.15169999259524</v>
       </c>
       <c r="Y7" t="n">
-        <v>99.14780000690372</v>
+        <v>48.98600000888109</v>
       </c>
       <c r="Z7" t="n">
         <v>0.0826692834568957</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="8">
@@ -3876,34 +5587,34 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15756684.9547489</v>
+        <v>15455190.24053487</v>
       </c>
       <c r="G8" t="n">
-        <v>22901195.10819018</v>
+        <v>21715319.34633613</v>
       </c>
       <c r="H8" t="n">
-        <v>22894352.11441293</v>
+        <v>21711082.22715314</v>
       </c>
       <c r="I8" t="n">
-        <v>524041.9958544513</v>
+        <v>509001.0649507</v>
       </c>
       <c r="J8" t="n">
-        <v>530884.9896317073</v>
+        <v>513238.1841336829</v>
       </c>
       <c r="K8" t="n">
-        <v>6812878.322897516</v>
+        <v>6838131.176331286</v>
       </c>
       <c r="L8" t="n">
-        <v>5518431.44154699</v>
+        <v>5538886.252828342</v>
       </c>
       <c r="M8" t="n">
-        <v>2071745.673049787</v>
+        <v>1233106.783984851</v>
       </c>
       <c r="N8" t="n">
-        <v>86340.98702297144</v>
+        <v>210672.3216537033</v>
       </c>
       <c r="O8" t="n">
-        <v>3313</v>
+        <v>7564</v>
       </c>
       <c r="P8" t="n">
         <v>1200</v>
@@ -3918,28 +5629,28 @@
         <v>1002</v>
       </c>
       <c r="T8" t="n">
-        <v>1670</v>
+        <v>3394</v>
       </c>
       <c r="U8" t="n">
-        <v>3968</v>
+        <v>3515</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>4.553900012979284</v>
+        <v>3.13730000925716</v>
       </c>
       <c r="X8" t="n">
-        <v>16.13932500913506</v>
+        <v>8.057125000050291</v>
       </c>
       <c r="Y8" t="n">
-        <v>161.5641000098549</v>
+        <v>45.34819998661988</v>
       </c>
       <c r="Z8" t="n">
         <v>0.0874769348802395</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="9">
@@ -3969,34 +5680,34 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>15769829.13243304</v>
+        <v>15465962.60412982</v>
       </c>
       <c r="G9" t="n">
-        <v>22898439.40855968</v>
+        <v>21712276.07168716</v>
       </c>
       <c r="H9" t="n">
-        <v>22894661.79263044</v>
+        <v>21711144.64020411</v>
       </c>
       <c r="I9" t="n">
-        <v>525616.9646313022</v>
+        <v>510875.4180425624</v>
       </c>
       <c r="J9" t="n">
-        <v>529394.5805605352</v>
+        <v>512006.8495256142</v>
       </c>
       <c r="K9" t="n">
-        <v>6799417.911288651</v>
+        <v>6822646.940177951</v>
       </c>
       <c r="L9" t="n">
-        <v>5507528.508143807</v>
+        <v>5526344.021544142</v>
       </c>
       <c r="M9" t="n">
-        <v>2074896.717123407</v>
+        <v>1233536.134352993</v>
       </c>
       <c r="N9" t="n">
-        <v>86353.65372001668</v>
+        <v>210394.0223251306</v>
       </c>
       <c r="O9" t="n">
-        <v>3314</v>
+        <v>7555</v>
       </c>
       <c r="P9" t="n">
         <v>1200</v>
@@ -4011,28 +5722,28 @@
         <v>1002</v>
       </c>
       <c r="T9" t="n">
-        <v>1672</v>
+        <v>3380</v>
       </c>
       <c r="U9" t="n">
-        <v>3981</v>
+        <v>3551</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>4.65884999721311</v>
+        <v>3.179850013111718</v>
       </c>
       <c r="X9" t="n">
-        <v>16.39664999675006</v>
+        <v>7.997725006134715</v>
       </c>
       <c r="Y9" t="n">
-        <v>122.6641999965068</v>
+        <v>31.45660000154749</v>
       </c>
       <c r="Z9" t="n">
         <v>0.08327562063373251</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="10">
@@ -4062,13 +5773,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>17141642.95871493</v>
+        <v>17300085.38600904</v>
       </c>
       <c r="G10" t="n">
-        <v>22959886.08385623</v>
+        <v>21776233.34357257</v>
       </c>
       <c r="H10" t="n">
-        <v>22959886.08385623</v>
+        <v>21776233.34357257</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4077,19 +5788,19 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>7167700.993786965</v>
+        <v>7263207.1273336</v>
       </c>
       <c r="L10" t="n">
-        <v>5805837.804967443</v>
+        <v>5883189.903731774</v>
       </c>
       <c r="M10" t="n">
-        <v>2275481.331899769</v>
+        <v>1523432.876555128</v>
       </c>
       <c r="N10" t="n">
-        <v>421444.2757462978</v>
+        <v>571095.0495217298</v>
       </c>
       <c r="O10" t="n">
-        <v>4721</v>
+        <v>7928</v>
       </c>
       <c r="P10" t="n">
         <v>1200</v>
@@ -4104,28 +5815,28 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1536</v>
+        <v>3402</v>
       </c>
       <c r="U10" t="n">
-        <v>4209</v>
+        <v>3479</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>3.73520000721328</v>
+        <v>2.31569999596104</v>
       </c>
       <c r="X10" t="n">
-        <v>6.607174989767373</v>
+        <v>4.061549996549729</v>
       </c>
       <c r="Y10" t="n">
-        <v>76.56620000489056</v>
+        <v>88.38609998929314</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="11">
@@ -4155,34 +5866,34 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15675332.93147962</v>
+        <v>15383049.8059842</v>
       </c>
       <c r="G11" t="n">
-        <v>22958283.1599208</v>
+        <v>21772124.67798623</v>
       </c>
       <c r="H11" t="n">
-        <v>22948107.06655229</v>
+        <v>21767421.14585574</v>
       </c>
       <c r="I11" t="n">
-        <v>522743.6584197714</v>
+        <v>509079.5969405894</v>
       </c>
       <c r="J11" t="n">
-        <v>532919.7517882928</v>
+        <v>513783.1290710877</v>
       </c>
       <c r="K11" t="n">
-        <v>7213833.513001338</v>
+        <v>7222414.959570932</v>
       </c>
       <c r="L11" t="n">
-        <v>5843205.145531084</v>
+        <v>5850156.117252456</v>
       </c>
       <c r="M11" t="n">
-        <v>2065043.310987359</v>
+        <v>1231491.66952704</v>
       </c>
       <c r="N11" t="n">
-        <v>86339.79815654384</v>
+        <v>211021.8302459966</v>
       </c>
       <c r="O11" t="n">
-        <v>3317</v>
+        <v>7541</v>
       </c>
       <c r="P11" t="n">
         <v>1200</v>
@@ -4197,28 +5908,28 @@
         <v>1002</v>
       </c>
       <c r="T11" t="n">
-        <v>1653</v>
+        <v>3380</v>
       </c>
       <c r="U11" t="n">
-        <v>4340</v>
+        <v>3712</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.674300009151921</v>
+        <v>2.362600003834814</v>
       </c>
       <c r="X11" t="n">
-        <v>6.418324999685865</v>
+        <v>3.886474994942546</v>
       </c>
       <c r="Y11" t="n">
-        <v>86.90329999080859</v>
+        <v>103.7788999965414</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
     <row r="12">
@@ -4248,13 +5959,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16018581.18991589</v>
+        <v>15812652.9828554</v>
       </c>
       <c r="G12" t="n">
-        <v>23492931.71470625</v>
+        <v>21893297.43909906</v>
       </c>
       <c r="H12" t="n">
-        <v>23492931.71470625</v>
+        <v>21893297.43909906</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4263,19 +5974,19 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>7075342.937771925</v>
+        <v>7052610.789910259</v>
       </c>
       <c r="L12" t="n">
-        <v>5731027.77959526</v>
+        <v>5712614.739827311</v>
       </c>
       <c r="M12" t="n">
-        <v>2527252.981103952</v>
+        <v>1383414.927305429</v>
       </c>
       <c r="N12" t="n">
-        <v>146211.4900243395</v>
+        <v>324302.3440246085</v>
       </c>
       <c r="O12" t="n">
-        <v>2765</v>
+        <v>7026</v>
       </c>
       <c r="P12" t="n">
         <v>1200</v>
@@ -4290,28 +6001,28 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2152</v>
+        <v>4046</v>
       </c>
       <c r="U12" t="n">
-        <v>4206</v>
+        <v>3766</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.714699996635318</v>
+        <v>2.472299995133653</v>
       </c>
       <c r="X12" t="n">
-        <v>6.488000006356742</v>
+        <v>4.042275009851437</v>
       </c>
       <c r="Y12" t="n">
-        <v>151.0854999942239</v>
+        <v>104.2315999802668</v>
       </c>
       <c r="Z12" t="n">
         <v>0.08327562063373251</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.8943155355954757</v>
+        <v>0.7694610778443114</v>
       </c>
     </row>
   </sheetData>
@@ -4338,7 +6049,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
@@ -4480,7 +6191,7 @@
         <v>6000</v>
       </c>
       <c r="H2" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -4489,22 +6200,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="L2" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="M2" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="N2" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="O2" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="P2" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="Q2" t="n">
         <v>1200</v>
@@ -4513,7 +6224,7 @@
         <v>10800</v>
       </c>
       <c r="S2" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -4546,31 +6257,31 @@
         <v>6000</v>
       </c>
       <c r="H3" t="n">
-        <v>14440441.25359564</v>
+        <v>14322473.61846223</v>
       </c>
       <c r="I3" t="n">
-        <v>-477060.2337897606</v>
+        <v>-463627.7349952646</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.197990187520172</v>
+        <v>-3.135564432519278</v>
       </c>
       <c r="K3" t="n">
-        <v>22546998.72552459</v>
+        <v>21767531.92473344</v>
       </c>
       <c r="L3" t="n">
-        <v>162341.1997658127</v>
+        <v>251361.8172715685</v>
       </c>
       <c r="M3" t="n">
-        <v>4649</v>
+        <v>6797</v>
       </c>
       <c r="N3" t="n">
-        <v>7243516.654348472</v>
+        <v>7168547.916091083</v>
       </c>
       <c r="O3" t="n">
-        <v>6519228.510898626</v>
+        <v>6451761.215571974</v>
       </c>
       <c r="P3" t="n">
-        <v>2023921.65910725</v>
+        <v>1560321.457496892</v>
       </c>
       <c r="Q3" t="n">
         <v>1200</v>
@@ -4579,7 +6290,7 @@
         <v>10800</v>
       </c>
       <c r="S3" t="n">
-        <v>10733.04194863498</v>
+        <v>10728.22568907883</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -4612,7 +6323,7 @@
         <v>2400</v>
       </c>
       <c r="H4" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -4621,22 +6332,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="L4" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="M4" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="N4" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="O4" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="P4" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="Q4" t="n">
         <v>1200</v>
@@ -4645,7 +6356,7 @@
         <v>10800</v>
       </c>
       <c r="S4" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -4678,7 +6389,7 @@
         <v>9600</v>
       </c>
       <c r="H5" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4687,22 +6398,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="L5" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="M5" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="N5" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="O5" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="P5" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="Q5" t="n">
         <v>1200</v>
@@ -4711,7 +6422,7 @@
         <v>10800</v>
       </c>
       <c r="S5" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -4744,31 +6455,31 @@
         <v>6000</v>
       </c>
       <c r="H6" t="n">
-        <v>15525067.2889435</v>
+        <v>15392912.44250014</v>
       </c>
       <c r="I6" t="n">
-        <v>607565.8015581015</v>
+        <v>606811.0890426487</v>
       </c>
       <c r="J6" t="n">
-        <v>4.072838887074171</v>
+        <v>4.103928916331667</v>
       </c>
       <c r="K6" t="n">
-        <v>23086047.07975373</v>
+        <v>22312621.20760542</v>
       </c>
       <c r="L6" t="n">
-        <v>161674.6884612505</v>
+        <v>251029.7094923189</v>
       </c>
       <c r="M6" t="n">
-        <v>4782</v>
+        <v>6963</v>
       </c>
       <c r="N6" t="n">
-        <v>5950634.162299372</v>
+        <v>5895896.887293483</v>
       </c>
       <c r="O6" t="n">
-        <v>4820044.225998992</v>
+        <v>4775707.960788722</v>
       </c>
       <c r="P6" t="n">
-        <v>2100776.122781828</v>
+        <v>1597110.771220959</v>
       </c>
       <c r="Q6" t="n">
         <v>960</v>
@@ -4777,7 +6488,7 @@
         <v>8640</v>
       </c>
       <c r="S6" t="n">
-        <v>8606.050514999999</v>
+        <v>8605.019909999999</v>
       </c>
       <c r="T6" t="b">
         <v>1</v>
@@ -4810,31 +6521,31 @@
         <v>6000</v>
       </c>
       <c r="H7" t="n">
-        <v>14381362.90292697</v>
+        <v>14267282.6979955</v>
       </c>
       <c r="I7" t="n">
-        <v>-536138.5844584331</v>
+        <v>-518818.6554619931</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.594024005372509</v>
+        <v>-3.508826586939873</v>
       </c>
       <c r="K7" t="n">
-        <v>22991712.68140488</v>
+        <v>22240398.93584402</v>
       </c>
       <c r="L7" t="n">
-        <v>161281.5413297225</v>
+        <v>250574.677136834</v>
       </c>
       <c r="M7" t="n">
-        <v>4630</v>
+        <v>6747</v>
       </c>
       <c r="N7" t="n">
-        <v>7928915.450676277</v>
+        <v>7877931.617286056</v>
       </c>
       <c r="O7" t="n">
-        <v>6423575.556374008</v>
+        <v>6381588.116233103</v>
       </c>
       <c r="P7" t="n">
-        <v>1922473.097948263</v>
+        <v>1457729.149787474</v>
       </c>
       <c r="Q7" t="n">
         <v>1440</v>
@@ -4843,7 +6554,7 @@
         <v>12960</v>
       </c>
       <c r="S7" t="n">
-        <v>11635.40022928571</v>
+        <v>11532.77695761905</v>
       </c>
       <c r="T7" t="b">
         <v>1</v>
@@ -4876,40 +6587,40 @@
         <v>6000</v>
       </c>
       <c r="H8" t="n">
-        <v>15031699.29842038</v>
+        <v>16318749.8972597</v>
       </c>
       <c r="I8" t="n">
-        <v>114197.8110349737</v>
+        <v>1532648.543802209</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7655290742323073</v>
+        <v>10.36546759125132</v>
       </c>
       <c r="K8" t="n">
-        <v>23018033.41401415</v>
+        <v>21852664.58695542</v>
       </c>
       <c r="L8" t="n">
-        <v>159343.4129742287</v>
+        <v>563286.3237157683</v>
       </c>
       <c r="M8" t="n">
-        <v>4570</v>
+        <v>8033</v>
       </c>
       <c r="N8" t="n">
-        <v>6795425.676098804</v>
+        <v>6932077.75110071</v>
       </c>
       <c r="O8" t="n">
-        <v>5505706.071095221</v>
+        <v>5624961.876708139</v>
       </c>
       <c r="P8" t="n">
-        <v>2111797.11024489</v>
+        <v>1520730.674759766</v>
       </c>
       <c r="Q8" t="n">
         <v>1200</v>
       </c>
       <c r="R8" t="n">
-        <v>10800</v>
+        <v>10762.55370335265</v>
       </c>
       <c r="S8" t="n">
-        <v>8928.540015</v>
+        <v>8919.929909999999</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -4942,40 +6653,40 @@
         <v>6000</v>
       </c>
       <c r="H9" t="n">
-        <v>15805180.4342615</v>
+        <v>14738026.27021217</v>
       </c>
       <c r="I9" t="n">
-        <v>887678.9468760956</v>
+        <v>-48075.08324532583</v>
       </c>
       <c r="J9" t="n">
-        <v>5.950587285858422</v>
+        <v>-0.3251369789514124</v>
       </c>
       <c r="K9" t="n">
-        <v>22709940.87859961</v>
+        <v>22390723.62614055</v>
       </c>
       <c r="L9" t="n">
-        <v>403733.9228706005</v>
+        <v>247951.1071310359</v>
       </c>
       <c r="M9" t="n">
-        <v>5982</v>
+        <v>6974</v>
       </c>
       <c r="N9" t="n">
-        <v>7521531.46381313</v>
+        <v>7133518.337195423</v>
       </c>
       <c r="O9" t="n">
-        <v>6099539.060000233</v>
+        <v>5778181.335209293</v>
       </c>
       <c r="P9" t="n">
-        <v>1779761.635225819</v>
+        <v>1557840.537460821</v>
       </c>
       <c r="Q9" t="n">
         <v>1200</v>
       </c>
       <c r="R9" t="n">
-        <v>10751.48977725521</v>
+        <v>10800</v>
       </c>
       <c r="S9" t="n">
-        <v>10265.47217628494</v>
+        <v>10765.01991</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -5008,7 +6719,7 @@
         <v>6000</v>
       </c>
       <c r="H10" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -5017,22 +6728,22 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="L10" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="M10" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="N10" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="O10" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="P10" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="Q10" t="n">
         <v>1200</v>
@@ -5041,7 +6752,7 @@
         <v>10800</v>
       </c>
       <c r="S10" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
       <c r="T10" t="b">
         <v>1</v>
@@ -5074,7 +6785,7 @@
         <v>6000</v>
       </c>
       <c r="H11" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -5083,22 +6794,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="L11" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="M11" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="N11" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="O11" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="P11" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="Q11" t="n">
         <v>1200</v>
@@ -5107,7 +6818,7 @@
         <v>10800</v>
       </c>
       <c r="S11" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
       <c r="T11" t="b">
         <v>1</v>
@@ -5138,7 +6849,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
@@ -5146,8 +6857,8 @@
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
@@ -5288,40 +6999,40 @@
         <v>6000</v>
       </c>
       <c r="I2" t="n">
-        <v>15007759.48123504</v>
+        <v>16632993.38339002</v>
       </c>
       <c r="J2" t="n">
-        <v>90257.99384964073</v>
+        <v>1846892.029932529</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6050476611379363</v>
+        <v>12.4907302187582</v>
       </c>
       <c r="L2" t="n">
-        <v>21722724.84883169</v>
+        <v>20890197.73884192</v>
       </c>
       <c r="M2" t="n">
-        <v>379073.2759704561</v>
+        <v>802907.6096831274</v>
       </c>
       <c r="N2" t="n">
-        <v>9281</v>
+        <v>12524</v>
       </c>
       <c r="O2" t="n">
-        <v>7039991.38093593</v>
+        <v>7101543.681620229</v>
       </c>
       <c r="P2" t="n">
-        <v>5702484.991709103</v>
+        <v>5762732.527131485</v>
       </c>
       <c r="Q2" t="n">
-        <v>1214898.105214339</v>
+        <v>891364.9688988267</v>
       </c>
       <c r="R2" t="n">
         <v>1200</v>
       </c>
       <c r="S2" t="n">
-        <v>10800</v>
+        <v>10763.29401295245</v>
       </c>
       <c r="T2" t="n">
-        <v>10697.80761</v>
+        <v>10173.54026628493</v>
       </c>
       <c r="U2" t="b">
         <v>1</v>
@@ -5357,31 +7068,31 @@
         <v>6000</v>
       </c>
       <c r="I3" t="n">
-        <v>15516587.91414978</v>
+        <v>14963927.62132196</v>
       </c>
       <c r="J3" t="n">
-        <v>599086.426764382</v>
+        <v>177826.2678644694</v>
       </c>
       <c r="K3" t="n">
-        <v>4.015997097576851</v>
+        <v>1.202658250566424</v>
       </c>
       <c r="L3" t="n">
-        <v>24639273.18188182</v>
+        <v>23447755.21566769</v>
       </c>
       <c r="M3" t="n">
-        <v>65585.1280950119</v>
+        <v>129010.4235452857</v>
       </c>
       <c r="N3" t="n">
-        <v>2248</v>
+        <v>4174</v>
       </c>
       <c r="O3" t="n">
-        <v>7227380.442651704</v>
+        <v>7179195.85590194</v>
       </c>
       <c r="P3" t="n">
-        <v>5854211.457168631</v>
+        <v>5815188.110193072</v>
       </c>
       <c r="Q3" t="n">
-        <v>3130087.69568599</v>
+        <v>2289896.889340529</v>
       </c>
       <c r="R3" t="n">
         <v>1200</v>
@@ -5390,7 +7101,7 @@
         <v>10800</v>
       </c>
       <c r="T3" t="n">
-        <v>10763.0015325</v>
+        <v>10756.147875</v>
       </c>
       <c r="U3" t="b">
         <v>1</v>
@@ -5426,31 +7137,31 @@
         <v>6000</v>
       </c>
       <c r="I4" t="n">
-        <v>16410328.12303822</v>
+        <v>15453352.15797146</v>
       </c>
       <c r="J4" t="n">
-        <v>1492826.635652818</v>
+        <v>667250.8045139704</v>
       </c>
       <c r="K4" t="n">
-        <v>10.00721626818799</v>
+        <v>4.512689238113099</v>
       </c>
       <c r="L4" t="n">
-        <v>26143620.1197607</v>
+        <v>24531683.51250007</v>
       </c>
       <c r="M4" t="n">
-        <v>28909.0888342084</v>
+        <v>71786.43934657144</v>
       </c>
       <c r="N4" t="n">
-        <v>1076</v>
+        <v>2488</v>
       </c>
       <c r="O4" t="n">
-        <v>7274653.788409699</v>
+        <v>7220800.525642404</v>
       </c>
       <c r="P4" t="n">
-        <v>5892478.996066857</v>
+        <v>5848866.077614348</v>
       </c>
       <c r="Q4" t="n">
-        <v>4259488.871711437</v>
+        <v>3051874.192016373</v>
       </c>
       <c r="R4" t="n">
         <v>1200</v>
@@ -5459,7 +7170,7 @@
         <v>10800</v>
       </c>
       <c r="T4" t="n">
-        <v>10789.52505</v>
+        <v>10780.38684</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
@@ -5495,7 +7206,7 @@
         <v>6000</v>
       </c>
       <c r="I5" t="n">
-        <v>14917501.4873854</v>
+        <v>14786101.35345749</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -5504,22 +7215,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>23165422.81918828</v>
+        <v>22382650.65499936</v>
       </c>
       <c r="M5" t="n">
-        <v>156695.8533883218</v>
+        <v>245483.2930631757</v>
       </c>
       <c r="N5" t="n">
-        <v>4675</v>
+        <v>6822</v>
       </c>
       <c r="O5" t="n">
-        <v>7163298.76431501</v>
+        <v>7112133.945271054</v>
       </c>
       <c r="P5" t="n">
-        <v>5802329.168881658</v>
+        <v>5760889.777650556</v>
       </c>
       <c r="Q5" t="n">
-        <v>2102608.015240967</v>
+        <v>1596110.942201504</v>
       </c>
       <c r="R5" t="n">
         <v>1200</v>
@@ -5528,7 +7239,7 @@
         <v>10800</v>
       </c>
       <c r="T5" t="n">
-        <v>10736.478015</v>
+        <v>10731.90891</v>
       </c>
       <c r="U5" t="b">
         <v>1</v>
